--- a/data/satisfaction_summary/2026/1-2月/1-2月客户类型满意度汇总表.xlsx
+++ b/data/satisfaction_summary/2026/1-2月/1-2月客户类型满意度汇总表.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.85</v>
+        <v>9.98</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
@@ -1080,13 +1080,13 @@
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>9.859999999999999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.6</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>9.67</v>
